--- a/product_selector_out/STM32G4x1.xlsx
+++ b/product_selector_out/STM32G4x1.xlsx
@@ -1974,7 +1974,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -13729,9 +13729,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -13794,14 +13794,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -13949,14 +13949,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY14" s="8" t="inlineStr">
@@ -14029,9 +14029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15691,9 +15691,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -15756,14 +15756,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -15911,14 +15911,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY20" s="8" t="inlineStr">
@@ -15991,9 +15991,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16018,9 +16018,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -16083,14 +16083,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -16238,14 +16238,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY21" s="8" t="inlineStr">
@@ -16318,9 +16318,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21250,9 +21250,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -21315,14 +21315,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
@@ -21470,14 +21470,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY37" s="8" t="inlineStr">
@@ -21550,9 +21550,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24607,7 +24607,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24673,7 +24673,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24702,12 +24702,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -24717,19 +24717,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24739,14 +24739,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24773,7 +24773,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -24783,19 +24783,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -24805,19 +24805,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -24827,19 +24827,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24849,19 +24849,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24871,19 +24871,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24893,14 +24893,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -24915,7 +24915,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24927,7 +24927,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24937,19 +24937,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24959,19 +24959,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24981,19 +24981,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -25015,7 +25015,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -25025,19 +25025,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25047,19 +25047,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -25069,19 +25069,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25091,7 +25091,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -25113,19 +25113,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25135,19 +25135,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25157,19 +25157,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25179,19 +25179,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25201,19 +25201,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25223,19 +25223,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25245,19 +25245,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25267,19 +25267,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25289,19 +25289,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25311,19 +25311,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -25333,19 +25333,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25355,19 +25355,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -25377,19 +25377,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -25399,19 +25399,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -25421,19 +25421,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -25443,19 +25443,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -25465,19 +25465,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -25487,19 +25487,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -25509,19 +25509,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -25531,19 +25531,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -25553,19 +25553,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -25575,19 +25575,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -25597,19 +25597,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -25619,19 +25619,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -25641,19 +25641,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -25663,19 +25663,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -25685,19 +25685,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -25707,19 +25707,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -25729,19 +25729,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -25751,19 +25751,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -25773,19 +25773,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -25795,19 +25795,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -25817,19 +25817,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -25839,19 +25839,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -25861,19 +25861,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -25883,19 +25883,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -25905,19 +25905,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -25927,19 +25927,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -25949,19 +25949,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -25971,19 +25971,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -25993,19 +25993,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -26015,19 +26015,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -26037,19 +26037,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -26059,19 +26059,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -26081,19 +26081,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -26103,19 +26103,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -26125,19 +26125,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -26147,19 +26147,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -26169,19 +26169,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -26191,19 +26191,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -26213,19 +26213,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -26235,19 +26235,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -26257,19 +26257,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -26279,19 +26279,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -26301,19 +26301,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -26323,19 +26323,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -26345,19 +26345,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -26367,19 +26367,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -26389,19 +26389,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -26411,19 +26411,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -26433,19 +26433,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -26455,19 +26455,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -26477,19 +26477,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -26499,19 +26499,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -26521,19 +26521,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -26543,19 +26543,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -26565,19 +26565,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -26587,19 +26587,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -26609,14 +26609,14 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -26631,14 +26631,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -26675,14 +26675,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -26704,7 +26704,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -26719,14 +26719,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -26748,7 +26748,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -26763,14 +26763,14 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -26792,7 +26792,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -26807,14 +26807,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -26851,14 +26851,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -26880,7 +26880,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -26895,14 +26895,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -26924,7 +26924,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -26939,14 +26939,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -26968,7 +26968,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -26983,14 +26983,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -27005,14 +27005,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -27027,14 +27027,14 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -27056,7 +27056,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -27071,14 +27071,14 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -27093,14 +27093,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -27115,14 +27115,14 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -27136,270 +27136,6 @@
         </is>
       </c>
       <c r="D119" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32G4x1.xlsx
+++ b/product_selector_out/STM32G4x1.xlsx
@@ -1974,7 +1974,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -13729,9 +13729,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -13794,14 +13794,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -13949,14 +13949,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY14" s="8" t="inlineStr">
@@ -14029,9 +14029,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -15691,9 +15691,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -15756,14 +15756,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -15911,14 +15911,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY20" s="8" t="inlineStr">
@@ -15991,9 +15991,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -16018,9 +16018,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -16083,14 +16083,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -16238,14 +16238,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY21" s="8" t="inlineStr">
@@ -16318,9 +16318,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -21250,9 +21250,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -21315,14 +21315,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T37" s="6" t="inlineStr">
@@ -21470,14 +21470,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY37" s="8" t="inlineStr">
@@ -21550,9 +21550,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24702,12 +24702,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -24717,19 +24717,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24739,14 +24739,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -24773,7 +24773,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -24783,19 +24783,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -24805,19 +24805,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -24827,19 +24827,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24849,19 +24849,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24871,19 +24871,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24893,14 +24893,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -24927,7 +24927,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -24937,19 +24937,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -24959,19 +24959,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -24981,19 +24981,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -25015,7 +25015,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -25025,19 +25025,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25047,19 +25047,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -25069,19 +25069,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25091,7 +25091,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -25113,19 +25113,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25135,19 +25135,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25157,19 +25157,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25179,19 +25179,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25201,19 +25201,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25223,19 +25223,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25245,19 +25245,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25267,19 +25267,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25289,19 +25289,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25311,19 +25311,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -25333,19 +25333,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25355,19 +25355,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -25377,19 +25377,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -25399,19 +25399,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -25421,19 +25421,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -25443,19 +25443,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -25465,19 +25465,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -25487,19 +25487,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -25509,19 +25509,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -25531,19 +25531,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -25553,19 +25553,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -25575,19 +25575,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -25597,19 +25597,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -25619,19 +25619,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -25641,19 +25641,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -25663,19 +25663,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -25685,19 +25685,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -25707,19 +25707,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -25729,19 +25729,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -25751,19 +25751,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -25773,19 +25773,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -25795,19 +25795,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -25817,19 +25817,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -25839,19 +25839,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -25861,19 +25861,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -25883,19 +25883,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -25905,19 +25905,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -25927,19 +25927,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -25949,19 +25949,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -25971,19 +25971,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -25993,19 +25993,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -26015,19 +26015,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -26037,19 +26037,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -26059,19 +26059,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -26081,19 +26081,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -26103,19 +26103,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -26125,19 +26125,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -26147,19 +26147,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -26169,19 +26169,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -26191,19 +26191,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -26213,19 +26213,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -26235,19 +26235,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -26257,19 +26257,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -26279,19 +26279,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -26301,19 +26301,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -26323,19 +26323,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -26345,19 +26345,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -26367,19 +26367,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -26389,19 +26389,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -26411,19 +26411,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -26433,19 +26433,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -26455,19 +26455,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -26477,19 +26477,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -26499,19 +26499,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -26521,19 +26521,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -26543,19 +26543,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -26565,19 +26565,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -26587,19 +26587,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -26609,14 +26609,14 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -26631,14 +26631,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -26682,7 +26682,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -26704,7 +26704,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -26719,14 +26719,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -26748,7 +26748,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -26770,7 +26770,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -26792,7 +26792,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -26807,14 +26807,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -26858,7 +26858,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -26880,7 +26880,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -26895,14 +26895,14 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -26924,7 +26924,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -26946,7 +26946,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -26968,7 +26968,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -26983,14 +26983,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -27005,14 +27005,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -27034,7 +27034,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -27056,7 +27056,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -27071,14 +27071,14 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -27093,14 +27093,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -27122,20 +27122,284 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>STM32G491CC</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32G4x1.xlsx
+++ b/product_selector_out/STM32G4x1.xlsx
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S24" s="4" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S28" s="4" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S31" s="4" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S33" s="4" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S34" s="4" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S36" s="4" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S38" s="4" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S39" s="4" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S40" s="4" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S41" s="4" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S42" s="4" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S43" s="4" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S44" s="4" t="inlineStr">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S45" s="4" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="R46" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S46" s="4" t="inlineStr">

--- a/product_selector_out/STM32G4x1.xlsx
+++ b/product_selector_out/STM32G4x1.xlsx
@@ -7076,7 +7076,7 @@
       </c>
       <c r="AM30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN30" s="4" t="inlineStr">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM31" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN31" s="4" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AM34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN34" s="4" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="AM43" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN43" s="4" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AM44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN44" s="4" t="inlineStr">
@@ -13572,9 +13572,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -14226,9 +14226,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -15207,9 +15207,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -15534,9 +15534,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -16515,9 +16515,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -16842,9 +16842,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -17169,9 +17169,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN24" s="6" t="inlineStr">
@@ -17496,9 +17496,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -17823,9 +17823,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN26" s="6" t="inlineStr">
@@ -18477,9 +18477,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -19131,9 +19131,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM30" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN30" s="6" t="inlineStr">
@@ -19458,9 +19458,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM31" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN31" s="6" t="inlineStr">
@@ -20112,9 +20112,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN33" s="6" t="inlineStr">
@@ -20439,9 +20439,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN34" s="6" t="inlineStr">
@@ -21093,9 +21093,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN36" s="6" t="inlineStr">
@@ -21747,9 +21747,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN38" s="6" t="inlineStr">
@@ -22074,9 +22074,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN39" s="6" t="inlineStr">
@@ -22728,9 +22728,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN41" s="6" t="inlineStr">
@@ -23382,9 +23382,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM43" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN43" s="6" t="inlineStr">
@@ -23709,9 +23709,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN44" s="6" t="inlineStr">

--- a/product_selector_out/STM32G4x1.xlsx
+++ b/product_selector_out/STM32G4x1.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM46"/>
+  <dimension ref="A1:BN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.984375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -9168,6 +9295,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -11130,6 +11287,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -11457,6 +11619,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -11784,6 +11951,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -12111,6 +12283,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -12438,12 +12615,17 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -12464,16 +12646,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -12486,6 +12666,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -12505,7 +12686,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -12557,7 +12740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM46"/>
+  <dimension ref="A1:BN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12625,6 +12808,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12958,6 +13142,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -13053,6 +13242,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -13375,7 +13565,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13702,7 +13897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14029,7 +14229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14356,7 +14561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14683,7 +14893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15010,7 +15225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15337,7 +15557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15664,7 +15889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15991,7 +16221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16318,7 +16553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16645,7 +16885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16972,7 +17217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17299,7 +17549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17626,7 +17881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17953,7 +18213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18280,7 +18545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18607,7 +18877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18934,7 +19209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19261,7 +19541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19588,7 +19873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19915,7 +20205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20242,7 +20537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20569,7 +20869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20896,7 +21201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21223,7 +21533,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21550,7 +21865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21877,7 +22197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22204,7 +22529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22531,7 +22861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22858,7 +23193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23185,7 +23525,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23512,7 +23857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23839,7 +24189,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24166,7 +24521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24493,7 +24853,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24501,8 +24866,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
